--- a/Code and data/Initial data/Sector data/TECH-BERD.xlsx
+++ b/Code and data/Initial data/Sector data/TECH-BERD.xlsx
@@ -3892,6 +3892,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F118">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3919,6 +3922,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F119">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3946,6 +3952,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F120">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3973,6 +3982,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F121">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4000,6 +4012,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F122">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4027,6 +4042,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F123">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4054,6 +4072,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F124">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4081,6 +4102,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F125">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4108,6 +4132,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F126">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4135,6 +4162,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F127">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4162,6 +4192,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F128">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4189,6 +4222,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F129">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4216,6 +4252,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F130">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4243,6 +4282,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F131">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4270,6 +4312,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F132">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4297,6 +4342,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F133">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4324,6 +4372,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F134">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4351,6 +4402,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F135">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4378,6 +4432,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F136">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4405,6 +4462,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F137">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4432,6 +4492,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F138">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4459,6 +4522,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F139">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4486,6 +4552,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F140">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4513,6 +4582,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F141">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4540,6 +4612,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F142">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4567,6 +4642,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F143">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4594,6 +4672,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F144">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4621,6 +4702,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F145">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4648,6 +4732,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F146">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4675,6 +4762,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F147">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4702,6 +4792,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F148">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4729,6 +4822,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F149">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4756,6 +4852,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F150">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4783,6 +4882,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F151">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4810,6 +4912,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F152">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4837,6 +4942,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F153">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4864,6 +4972,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F154">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4891,6 +5002,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F155">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4918,6 +5032,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F156">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4945,6 +5062,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F157">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4972,6 +5092,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F158">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4999,6 +5122,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F159">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5026,6 +5152,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F160">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5053,6 +5182,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F161">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5080,6 +5212,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F162">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5107,6 +5242,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F163">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5134,6 +5272,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F164">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5161,6 +5302,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F165">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5188,6 +5332,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F166">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5215,6 +5362,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F167">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5242,6 +5392,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F168">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5269,6 +5422,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F169">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5296,6 +5452,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F170">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5323,6 +5482,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F171">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5350,6 +5512,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F172">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5377,6 +5542,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F173">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5404,6 +5572,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F174">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -5431,6 +5602,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F175">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -5458,6 +5632,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F176">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -5485,6 +5662,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F177">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -5512,6 +5692,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F178">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -5539,6 +5722,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F179">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -5566,6 +5752,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F180">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -5593,6 +5782,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F181">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -5620,6 +5812,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F182">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -5647,6 +5842,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F183">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -5674,6 +5872,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F184">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -5701,6 +5902,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F185">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -5728,6 +5932,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F186">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -5755,6 +5962,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F187">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -5782,6 +5992,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F188">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -5809,6 +6022,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F189">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -5836,6 +6052,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F190">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -5863,6 +6082,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F191">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -5890,6 +6112,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F192">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -5917,6 +6142,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F193">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -5944,6 +6172,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F194">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -5971,6 +6202,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F195">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -5998,6 +6232,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F196">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6025,6 +6262,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F197">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6052,6 +6292,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F198">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6079,6 +6322,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F199">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6106,6 +6352,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F200">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6133,6 +6382,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F201">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6160,6 +6412,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F202">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -6187,6 +6442,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F203">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -6214,6 +6472,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F204">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -6241,6 +6502,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F205">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -6268,6 +6532,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F206">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -6295,6 +6562,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F207">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -6322,6 +6592,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F208">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -6349,6 +6622,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F209">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -6376,6 +6652,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F210">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -6403,6 +6682,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F211">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -6430,6 +6712,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F212">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -6457,6 +6742,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F213">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -6484,6 +6772,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F214">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -6511,6 +6802,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F215">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -6538,6 +6832,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F216">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -6565,6 +6862,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F217">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -6592,6 +6892,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F218">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -6619,6 +6922,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F219">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -6646,6 +6952,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F220">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -6673,6 +6982,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F221">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -6700,6 +7012,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F222">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -6727,6 +7042,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F223">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -6754,6 +7072,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F224">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -6781,6 +7102,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F225">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -6808,6 +7132,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F226">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -6835,6 +7162,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F227">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -6862,6 +7192,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F228">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -6889,6 +7222,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F229">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -6916,6 +7252,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F230">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -6943,6 +7282,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F231">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -6970,6 +7312,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F232">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -6997,6 +7342,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F233">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -7024,6 +7372,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F234">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -7051,6 +7402,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F235">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -7078,6 +7432,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F236">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -7105,6 +7462,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F237">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -38602,6 +38962,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F1287">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="1288">
       <c r="A1288" t="inlineStr">
@@ -38629,6 +38992,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F1288">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="1289">
       <c r="A1289" t="inlineStr">
@@ -38656,6 +39022,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F1289">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="1290">
       <c r="A1290" t="inlineStr">
@@ -38683,6 +39052,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F1290">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="1291">
       <c r="A1291" t="inlineStr">
@@ -38710,6 +39082,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F1291">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="1292">
       <c r="A1292" t="inlineStr">
@@ -38737,6 +39112,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F1292">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="1293">
       <c r="A1293" t="inlineStr">
@@ -38764,6 +39142,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F1293">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="1294">
       <c r="A1294" t="inlineStr">
@@ -38791,6 +39172,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F1294">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="1295">
       <c r="A1295" t="inlineStr">
@@ -38818,6 +39202,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F1295">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="1296">
       <c r="A1296" t="inlineStr">
@@ -38845,6 +39232,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F1296">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="1297">
       <c r="A1297" t="inlineStr">
@@ -38872,6 +39262,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F1297">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="1298">
       <c r="A1298" t="inlineStr">
@@ -38899,6 +39292,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F1298">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="1299">
       <c r="A1299" t="inlineStr">
@@ -38926,6 +39322,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F1299">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="1300">
       <c r="A1300" t="inlineStr">
@@ -38953,6 +39352,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F1300">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="1301">
       <c r="A1301" t="inlineStr">
@@ -38980,6 +39382,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F1301">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="1302">
       <c r="A1302" t="inlineStr">
@@ -39007,6 +39412,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F1302">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="1303">
       <c r="A1303" t="inlineStr">
@@ -39034,6 +39442,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F1303">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="1304">
       <c r="A1304" t="inlineStr">
@@ -39061,6 +39472,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F1304">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="1305">
       <c r="A1305" t="inlineStr">
@@ -39088,6 +39502,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F1305">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="1306">
       <c r="A1306" t="inlineStr">
@@ -39115,6 +39532,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F1306">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="1307">
       <c r="A1307" t="inlineStr">
@@ -39142,6 +39562,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F1307">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="1308">
       <c r="A1308" t="inlineStr">
@@ -39169,6 +39592,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F1308">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="1309">
       <c r="A1309" t="inlineStr">
@@ -39196,6 +39622,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F1309">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="1310">
       <c r="A1310" t="inlineStr">
@@ -39223,6 +39652,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F1310">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="1311">
       <c r="A1311" t="inlineStr">
@@ -63940,6 +64372,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2134">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2135">
       <c r="A2135" t="inlineStr">
@@ -63967,6 +64402,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2135">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2136">
       <c r="A2136" t="inlineStr">
@@ -63994,6 +64432,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2136">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2137">
       <c r="A2137" t="inlineStr">
@@ -64021,6 +64462,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2137">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2138">
       <c r="A2138" t="inlineStr">
@@ -64048,6 +64492,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2138">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2139">
       <c r="A2139" t="inlineStr">
@@ -64075,6 +64522,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2139">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2140">
       <c r="A2140" t="inlineStr">
@@ -64102,6 +64552,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2140">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2141">
       <c r="A2141" t="inlineStr">
@@ -64129,6 +64582,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2141">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2142">
       <c r="A2142" t="inlineStr">
@@ -64156,6 +64612,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2142">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2143">
       <c r="A2143" t="inlineStr">
@@ -64183,6 +64642,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2143">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2144">
       <c r="A2144" t="inlineStr">
@@ -64210,6 +64672,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2144">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2145">
       <c r="A2145" t="inlineStr">
@@ -64237,6 +64702,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2145">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2146">
       <c r="A2146" t="inlineStr">
@@ -64264,6 +64732,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2146">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2147">
       <c r="A2147" t="inlineStr">
@@ -64291,6 +64762,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2147">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2148">
       <c r="A2148" t="inlineStr">
@@ -64318,6 +64792,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2148">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2149">
       <c r="A2149" t="inlineStr">
@@ -64345,6 +64822,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2149">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2150">
       <c r="A2150" t="inlineStr">
@@ -64372,6 +64852,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2150">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2151">
       <c r="A2151" t="inlineStr">
@@ -64399,6 +64882,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2151">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2152">
       <c r="A2152" t="inlineStr">
@@ -64426,6 +64912,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2152">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2153">
       <c r="A2153" t="inlineStr">
@@ -64453,6 +64942,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2153">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2154">
       <c r="A2154" t="inlineStr">
@@ -64480,6 +64972,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2154">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2155">
       <c r="A2155" t="inlineStr">
@@ -64507,6 +65002,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2155">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2156">
       <c r="A2156" t="inlineStr">
@@ -64534,6 +65032,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2156">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2157">
       <c r="A2157" t="inlineStr">
@@ -64561,6 +65062,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2157">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2158">
       <c r="A2158" t="inlineStr">
@@ -64588,6 +65092,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2158">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2159">
       <c r="A2159" t="inlineStr">
@@ -64615,6 +65122,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2159">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2160">
       <c r="A2160" t="inlineStr">
@@ -64642,6 +65152,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2160">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2161">
       <c r="A2161" t="inlineStr">
@@ -64669,6 +65182,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2161">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2162">
       <c r="A2162" t="inlineStr">
@@ -64696,6 +65212,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2162">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2163">
       <c r="A2163" t="inlineStr">
@@ -64723,6 +65242,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2163">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2164">
       <c r="A2164" t="inlineStr">
@@ -64750,6 +65272,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2164">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2165">
       <c r="A2165" t="inlineStr">
@@ -64777,6 +65302,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2165">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2166">
       <c r="A2166" t="inlineStr">
@@ -64804,6 +65332,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2166">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2167">
       <c r="A2167" t="inlineStr">
@@ -64831,6 +65362,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2167">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2168">
       <c r="A2168" t="inlineStr">
@@ -64858,6 +65392,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2168">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2169">
       <c r="A2169" t="inlineStr">
@@ -64885,6 +65422,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2169">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2170">
       <c r="A2170" t="inlineStr">
@@ -64912,6 +65452,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2170">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2171">
       <c r="A2171" t="inlineStr">
@@ -64939,6 +65482,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2171">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2172">
       <c r="A2172" t="inlineStr">
@@ -64966,6 +65512,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2172">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2173">
       <c r="A2173" t="inlineStr">
@@ -64993,6 +65542,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2173">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2174">
       <c r="A2174" t="inlineStr">
@@ -65020,6 +65572,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2174">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2175">
       <c r="A2175" t="inlineStr">
@@ -65047,6 +65602,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2175">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2176">
       <c r="A2176" t="inlineStr">
@@ -65074,6 +65632,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2176">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2177">
       <c r="A2177" t="inlineStr">
@@ -65101,6 +65662,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2177">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2178">
       <c r="A2178" t="inlineStr">
@@ -65128,6 +65692,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2178">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2179">
       <c r="A2179" t="inlineStr">
@@ -65155,6 +65722,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2179">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2180">
       <c r="A2180" t="inlineStr">
@@ -65182,6 +65752,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2180">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2181">
       <c r="A2181" t="inlineStr">
@@ -65209,6 +65782,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2181">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2182">
       <c r="A2182" t="inlineStr">
@@ -65236,6 +65812,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2182">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2183">
       <c r="A2183" t="inlineStr">
@@ -65263,6 +65842,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2183">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2184">
       <c r="A2184" t="inlineStr">
@@ -65290,6 +65872,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2184">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2185">
       <c r="A2185" t="inlineStr">
@@ -65317,6 +65902,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2185">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2186">
       <c r="A2186" t="inlineStr">
@@ -65344,6 +65932,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2186">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2187">
       <c r="A2187" t="inlineStr">
@@ -65371,6 +65962,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2187">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2188">
       <c r="A2188" t="inlineStr">
@@ -65398,6 +65992,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2188">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2189">
       <c r="A2189" t="inlineStr">
@@ -65425,6 +66022,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2189">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2190">
       <c r="A2190" t="inlineStr">
@@ -65452,6 +66052,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2190">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2191">
       <c r="A2191" t="inlineStr">
@@ -65479,6 +66082,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2191">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2192">
       <c r="A2192" t="inlineStr">
@@ -65506,6 +66112,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2192">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2193">
       <c r="A2193" t="inlineStr">
@@ -65533,6 +66142,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2193">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2194">
       <c r="A2194" t="inlineStr">
@@ -65560,6 +66172,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2194">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2195">
       <c r="A2195" t="inlineStr">
@@ -65587,6 +66202,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2195">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2196">
       <c r="A2196" t="inlineStr">
@@ -65614,6 +66232,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2196">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2197">
       <c r="A2197" t="inlineStr">
@@ -65641,6 +66262,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2197">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2198">
       <c r="A2198" t="inlineStr">
@@ -65668,6 +66292,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2198">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2199">
       <c r="A2199" t="inlineStr">
@@ -65695,6 +66322,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2199">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2200">
       <c r="A2200" t="inlineStr">
@@ -65722,6 +66352,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2200">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2201">
       <c r="A2201" t="inlineStr">
@@ -65749,6 +66382,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2201">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2202">
       <c r="A2202" t="inlineStr">
@@ -65776,6 +66412,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2202">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2203">
       <c r="A2203" t="inlineStr">
@@ -65803,6 +66442,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2203">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2204">
       <c r="A2204" t="inlineStr">
@@ -65830,6 +66472,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2204">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2205">
       <c r="A2205" t="inlineStr">
@@ -65857,6 +66502,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2205">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2206">
       <c r="A2206" t="inlineStr">
@@ -65884,6 +66532,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2206">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2207">
       <c r="A2207" t="inlineStr">
@@ -65911,6 +66562,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2207">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2208">
       <c r="A2208" t="inlineStr">
@@ -65938,6 +66592,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2208">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2209">
       <c r="A2209" t="inlineStr">
@@ -65965,6 +66622,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2209">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2210">
       <c r="A2210" t="inlineStr">
@@ -65992,6 +66652,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2210">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2211">
       <c r="A2211" t="inlineStr">
@@ -66019,6 +66682,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2211">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2212">
       <c r="A2212" t="inlineStr">
@@ -66046,6 +66712,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2212">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2213">
       <c r="A2213" t="inlineStr">
@@ -66073,6 +66742,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2213">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2214">
       <c r="A2214" t="inlineStr">
@@ -66100,6 +66772,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2214">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2215">
       <c r="A2215" t="inlineStr">
@@ -66127,6 +66802,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2215">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2216">
       <c r="A2216" t="inlineStr">
@@ -66154,6 +66832,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2216">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2217">
       <c r="A2217" t="inlineStr">
@@ -66181,6 +66862,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2217">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2218">
       <c r="A2218" t="inlineStr">
@@ -66208,6 +66892,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2218">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2219">
       <c r="A2219" t="inlineStr">
@@ -66235,6 +66922,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2219">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2220">
       <c r="A2220" t="inlineStr">
@@ -66262,6 +66952,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2220">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2221">
       <c r="A2221" t="inlineStr">
@@ -66289,6 +66982,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2221">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2222">
       <c r="A2222" t="inlineStr">
@@ -66316,6 +67012,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2222">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2223">
       <c r="A2223" t="inlineStr">
@@ -66343,6 +67042,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2223">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2224">
       <c r="A2224" t="inlineStr">
@@ -66370,6 +67072,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2224">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2225">
       <c r="A2225" t="inlineStr">
@@ -66397,6 +67102,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2225">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2226">
       <c r="A2226" t="inlineStr">
@@ -66424,6 +67132,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2226">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2227">
       <c r="A2227" t="inlineStr">
@@ -66451,6 +67162,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2227">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2228">
       <c r="A2228" t="inlineStr">
@@ -66478,6 +67192,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2228">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2229">
       <c r="A2229" t="inlineStr">
@@ -66505,6 +67222,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2229">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2230">
       <c r="A2230" t="inlineStr">
@@ -66532,6 +67252,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2230">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2231">
       <c r="A2231" t="inlineStr">
@@ -66559,6 +67282,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2231">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2232">
       <c r="A2232" t="inlineStr">
@@ -66586,6 +67312,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2232">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2233">
       <c r="A2233" t="inlineStr">
@@ -66613,6 +67342,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2233">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2234">
       <c r="A2234" t="inlineStr">
@@ -66640,6 +67372,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2234">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2235">
       <c r="A2235" t="inlineStr">
@@ -66667,6 +67402,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2235">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2236">
       <c r="A2236" t="inlineStr">
@@ -66694,6 +67432,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2236">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2237">
       <c r="A2237" t="inlineStr">
@@ -66721,6 +67462,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2237">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2238">
       <c r="A2238" t="inlineStr">
@@ -66748,6 +67492,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2238">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2239">
       <c r="A2239" t="inlineStr">
@@ -66775,6 +67522,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2239">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2240">
       <c r="A2240" t="inlineStr">
@@ -66802,6 +67552,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2240">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2241">
       <c r="A2241" t="inlineStr">
@@ -66829,6 +67582,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2241">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2242">
       <c r="A2242" t="inlineStr">
@@ -66856,6 +67612,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2242">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2243">
       <c r="A2243" t="inlineStr">
@@ -66883,6 +67642,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2243">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2244">
       <c r="A2244" t="inlineStr">
@@ -66910,6 +67672,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2244">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2245">
       <c r="A2245" t="inlineStr">
@@ -66937,6 +67702,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2245">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2246">
       <c r="A2246" t="inlineStr">
@@ -66964,6 +67732,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2246">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2247">
       <c r="A2247" t="inlineStr">
@@ -66991,6 +67762,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2247">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2248">
       <c r="A2248" t="inlineStr">
@@ -67018,6 +67792,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2248">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2249">
       <c r="A2249" t="inlineStr">
@@ -67045,6 +67822,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2249">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2250">
       <c r="A2250" t="inlineStr">
@@ -67072,6 +67852,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2250">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2251">
       <c r="A2251" t="inlineStr">
@@ -67099,6 +67882,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2251">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2252">
       <c r="A2252" t="inlineStr">
@@ -67126,6 +67912,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2252">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2253">
       <c r="A2253" t="inlineStr">
@@ -67153,6 +67942,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2253">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2254">
       <c r="A2254" t="inlineStr">
@@ -67180,6 +67972,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2254">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2255">
       <c r="A2255" t="inlineStr">
@@ -67207,6 +68002,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2255">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2256">
       <c r="A2256" t="inlineStr">
@@ -67234,6 +68032,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2256">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2257">
       <c r="A2257" t="inlineStr">
@@ -67261,6 +68062,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2257">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2258">
       <c r="A2258" t="inlineStr">
@@ -67288,6 +68092,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2258">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2259">
       <c r="A2259" t="inlineStr">
@@ -67315,6 +68122,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2259">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2260">
       <c r="A2260" t="inlineStr">
@@ -67342,6 +68152,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2260">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2261">
       <c r="A2261" t="inlineStr">
@@ -67369,6 +68182,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2261">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2262">
       <c r="A2262" t="inlineStr">
@@ -67396,6 +68212,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2262">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2263">
       <c r="A2263" t="inlineStr">
@@ -67423,6 +68242,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2263">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2264">
       <c r="A2264" t="inlineStr">
@@ -67450,6 +68272,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2264">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2265">
       <c r="A2265" t="inlineStr">
@@ -67477,6 +68302,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2265">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2266">
       <c r="A2266" t="inlineStr">
@@ -67504,6 +68332,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2266">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2267">
       <c r="A2267" t="inlineStr">
@@ -67531,6 +68362,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2267">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2268">
       <c r="A2268" t="inlineStr">
@@ -67558,6 +68392,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2268">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2269">
       <c r="A2269" t="inlineStr">
@@ -67585,6 +68422,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2269">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2270">
       <c r="A2270" t="inlineStr">
@@ -67612,6 +68452,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2270">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2271">
       <c r="A2271" t="inlineStr">
@@ -67639,6 +68482,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2271">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="2272">
       <c r="A2272" t="inlineStr">
@@ -69106,6 +69952,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2320">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="2321">
       <c r="A2321" t="inlineStr">
@@ -69133,6 +69982,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2321">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="2322">
       <c r="A2322" t="inlineStr">
@@ -69160,6 +70012,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2322">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="2323">
       <c r="A2323" t="inlineStr">
@@ -69187,6 +70042,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2323">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="2324">
       <c r="A2324" t="inlineStr">
@@ -69214,6 +70072,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2324">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="2325">
       <c r="A2325" t="inlineStr">
@@ -69241,6 +70102,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2325">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="2326">
       <c r="A2326" t="inlineStr">
@@ -69268,6 +70132,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2326">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="2327">
       <c r="A2327" t="inlineStr">
@@ -69295,6 +70162,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2327">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="2328">
       <c r="A2328" t="inlineStr">
@@ -69322,6 +70192,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2328">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="2329">
       <c r="A2329" t="inlineStr">
@@ -69349,6 +70222,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2329">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="2330">
       <c r="A2330" t="inlineStr">
@@ -69376,6 +70252,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2330">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="2331">
       <c r="A2331" t="inlineStr">
@@ -69403,6 +70282,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2331">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="2332">
       <c r="A2332" t="inlineStr">
@@ -70510,6 +71392,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2368">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="2369">
       <c r="A2369" t="inlineStr">
@@ -70537,6 +71422,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2369">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="2370">
       <c r="A2370" t="inlineStr">
@@ -70564,6 +71452,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2370">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="2371">
       <c r="A2371" t="inlineStr">
@@ -70591,6 +71482,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2371">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="2372">
       <c r="A2372" t="inlineStr">
@@ -70618,6 +71512,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2372">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="2373">
       <c r="A2373" t="inlineStr">
@@ -70645,6 +71542,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2373">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="2374">
       <c r="A2374" t="inlineStr">
@@ -70672,6 +71572,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2374">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="2375">
       <c r="A2375" t="inlineStr">
@@ -70699,6 +71602,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2375">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="2376">
       <c r="A2376" t="inlineStr">
@@ -70726,6 +71632,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2376">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="2377">
       <c r="A2377" t="inlineStr">
@@ -70753,6 +71662,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2377">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="2378">
       <c r="A2378" t="inlineStr">
@@ -70780,6 +71692,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2378">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="2379">
       <c r="A2379" t="inlineStr">
@@ -70807,6 +71722,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2379">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="2380">
       <c r="A2380" t="inlineStr">
@@ -74404,6 +75322,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2499">
+        <v>0.8100000000000001</v>
+      </c>
     </row>
     <row r="2500">
       <c r="A2500" t="inlineStr">
@@ -74431,6 +75352,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2500">
+        <v>0.8100000000000001</v>
+      </c>
     </row>
     <row r="2501">
       <c r="A2501" t="inlineStr">
@@ -74458,6 +75382,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2501">
+        <v>0.8100000000000001</v>
+      </c>
     </row>
     <row r="2502">
       <c r="A2502" t="inlineStr">
@@ -74485,6 +75412,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2502">
+        <v>0.8100000000000001</v>
+      </c>
     </row>
     <row r="2503">
       <c r="A2503" t="inlineStr">
@@ -74512,6 +75442,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2503">
+        <v>0.8100000000000001</v>
+      </c>
     </row>
     <row r="2504">
       <c r="A2504" t="inlineStr">
@@ -74539,6 +75472,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2504">
+        <v>0.8100000000000001</v>
+      </c>
     </row>
     <row r="2505">
       <c r="A2505" t="inlineStr">
@@ -74566,6 +75502,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2505">
+        <v>0.8100000000000001</v>
+      </c>
     </row>
     <row r="2506">
       <c r="A2506" t="inlineStr">
@@ -74593,6 +75532,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2506">
+        <v>0.8100000000000001</v>
+      </c>
     </row>
     <row r="2507">
       <c r="A2507" t="inlineStr">
@@ -74620,6 +75562,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2507">
+        <v>0.8100000000000001</v>
+      </c>
     </row>
     <row r="2508">
       <c r="A2508" t="inlineStr">
@@ -74647,6 +75592,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2508">
+        <v>0.8100000000000001</v>
+      </c>
     </row>
     <row r="2509">
       <c r="A2509" t="inlineStr">
@@ -74674,6 +75622,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2509">
+        <v>0.8100000000000001</v>
+      </c>
     </row>
     <row r="2510">
       <c r="A2510" t="inlineStr">
@@ -74701,6 +75652,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2510">
+        <v>0.8100000000000001</v>
+      </c>
     </row>
     <row r="2511">
       <c r="A2511" t="inlineStr">
@@ -74728,6 +75682,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2511">
+        <v>1.08</v>
+      </c>
     </row>
     <row r="2512">
       <c r="A2512" t="inlineStr">
@@ -74755,6 +75712,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2512">
+        <v>1.08</v>
+      </c>
     </row>
     <row r="2513">
       <c r="A2513" t="inlineStr">
@@ -74782,6 +75742,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2513">
+        <v>1.08</v>
+      </c>
     </row>
     <row r="2514">
       <c r="A2514" t="inlineStr">
@@ -74809,6 +75772,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2514">
+        <v>1.08</v>
+      </c>
     </row>
     <row r="2515">
       <c r="A2515" t="inlineStr">
@@ -74836,6 +75802,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2515">
+        <v>1.08</v>
+      </c>
     </row>
     <row r="2516">
       <c r="A2516" t="inlineStr">
@@ -74863,6 +75832,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2516">
+        <v>1.08</v>
+      </c>
     </row>
     <row r="2517">
       <c r="A2517" t="inlineStr">
@@ -74890,6 +75862,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2517">
+        <v>1.08</v>
+      </c>
     </row>
     <row r="2518">
       <c r="A2518" t="inlineStr">
@@ -74917,6 +75892,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2518">
+        <v>1.08</v>
+      </c>
     </row>
     <row r="2519">
       <c r="A2519" t="inlineStr">
@@ -74944,6 +75922,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2519">
+        <v>1.08</v>
+      </c>
     </row>
     <row r="2520">
       <c r="A2520" t="inlineStr">
@@ -74971,6 +75952,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2520">
+        <v>1.08</v>
+      </c>
     </row>
     <row r="2521">
       <c r="A2521" t="inlineStr">
@@ -74998,6 +75982,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2521">
+        <v>1.08</v>
+      </c>
     </row>
     <row r="2522">
       <c r="A2522" t="inlineStr">
@@ -75025,6 +76012,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2522">
+        <v>1.08</v>
+      </c>
     </row>
     <row r="2523">
       <c r="A2523" t="inlineStr">
@@ -75052,6 +76042,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2523">
+        <v>0.58</v>
+      </c>
     </row>
     <row r="2524">
       <c r="A2524" t="inlineStr">
@@ -75079,6 +76072,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2524">
+        <v>0.58</v>
+      </c>
     </row>
     <row r="2525">
       <c r="A2525" t="inlineStr">
@@ -75106,6 +76102,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2525">
+        <v>0.58</v>
+      </c>
     </row>
     <row r="2526">
       <c r="A2526" t="inlineStr">
@@ -75133,6 +76132,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2526">
+        <v>0.58</v>
+      </c>
     </row>
     <row r="2527">
       <c r="A2527" t="inlineStr">
@@ -75160,6 +76162,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2527">
+        <v>0.58</v>
+      </c>
     </row>
     <row r="2528">
       <c r="A2528" t="inlineStr">
@@ -75187,6 +76192,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2528">
+        <v>0.58</v>
+      </c>
     </row>
     <row r="2529">
       <c r="A2529" t="inlineStr">
@@ -75214,6 +76222,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2529">
+        <v>0.58</v>
+      </c>
     </row>
     <row r="2530">
       <c r="A2530" t="inlineStr">
@@ -75241,6 +76252,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2530">
+        <v>0.58</v>
+      </c>
     </row>
     <row r="2531">
       <c r="A2531" t="inlineStr">
@@ -75268,6 +76282,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2531">
+        <v>0.58</v>
+      </c>
     </row>
     <row r="2532">
       <c r="A2532" t="inlineStr">
@@ -75295,6 +76312,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2532">
+        <v>0.58</v>
+      </c>
     </row>
     <row r="2533">
       <c r="A2533" t="inlineStr">
@@ -75322,6 +76342,9 @@
           <t>R&amp;D, % of regional GDP</t>
         </is>
       </c>
+      <c r="F2533">
+        <v>0.58</v>
+      </c>
     </row>
     <row r="2534">
       <c r="A2534" t="inlineStr">
@@ -75348,6 +76371,9 @@
         <is>
           <t>R&amp;D, % of regional GDP</t>
         </is>
+      </c>
+      <c r="F2534">
+        <v>0.58</v>
       </c>
     </row>
     <row r="2535">
